--- a/artfynd/A 39136-2021 artfynd.xlsx
+++ b/artfynd/A 39136-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119718203</v>
+        <v>119718208</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576877</v>
+        <v>576868</v>
       </c>
       <c r="R2" t="n">
-        <v>6509760</v>
+        <v>6509665</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119718208</v>
+        <v>119718204</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576868</v>
+        <v>576855</v>
       </c>
       <c r="R3" t="n">
-        <v>6509665</v>
+        <v>6509782</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119718204</v>
+        <v>119718220</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>94574</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576855</v>
+        <v>576829</v>
       </c>
       <c r="R4" t="n">
-        <v>6509782</v>
+        <v>6509757</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119718220</v>
+        <v>119718203</v>
       </c>
       <c r="B5" t="n">
-        <v>94574</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576829</v>
+        <v>576877</v>
       </c>
       <c r="R5" t="n">
-        <v>6509757</v>
+        <v>6509760</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 39136-2021 artfynd.xlsx
+++ b/artfynd/A 39136-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119718208</v>
+        <v>119718204</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576868</v>
+        <v>576855</v>
       </c>
       <c r="R2" t="n">
-        <v>6509665</v>
+        <v>6509782</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119718204</v>
+        <v>119718220</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>94574</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576855</v>
+        <v>576829</v>
       </c>
       <c r="R3" t="n">
-        <v>6509782</v>
+        <v>6509757</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119718220</v>
+        <v>119718203</v>
       </c>
       <c r="B4" t="n">
-        <v>94574</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576829</v>
+        <v>576877</v>
       </c>
       <c r="R4" t="n">
-        <v>6509757</v>
+        <v>6509760</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119718203</v>
+        <v>119718208</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>8432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576877</v>
+        <v>576868</v>
       </c>
       <c r="R5" t="n">
-        <v>6509760</v>
+        <v>6509665</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 39136-2021 artfynd.xlsx
+++ b/artfynd/A 39136-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119718204</v>
+        <v>119718203</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576855</v>
+        <v>576877</v>
       </c>
       <c r="R2" t="n">
-        <v>6509782</v>
+        <v>6509760</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119718203</v>
+        <v>119718204</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576877</v>
+        <v>576855</v>
       </c>
       <c r="R4" t="n">
-        <v>6509760</v>
+        <v>6509782</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 39136-2021 artfynd.xlsx
+++ b/artfynd/A 39136-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119718203</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119718220</v>
+        <v>119718208</v>
       </c>
       <c r="B3" t="n">
-        <v>94574</v>
+        <v>8432</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576829</v>
+        <v>576868</v>
       </c>
       <c r="R3" t="n">
-        <v>6509757</v>
+        <v>6509665</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -882,7 +882,7 @@
         <v>119718204</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119718208</v>
+        <v>119718220</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
+        <v>94597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576868</v>
+        <v>576829</v>
       </c>
       <c r="R5" t="n">
-        <v>6509665</v>
+        <v>6509757</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 39136-2021 artfynd.xlsx
+++ b/artfynd/A 39136-2021 artfynd.xlsx
@@ -780,12 +780,7 @@
         <v>119718208</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,6 +806,15 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strupen, Ög</t>

--- a/artfynd/A 39136-2021 artfynd.xlsx
+++ b/artfynd/A 39136-2021 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>119718208</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39136-2021 artfynd.xlsx
+++ b/artfynd/A 39136-2021 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119718203</v>
+        <v>119718220</v>
       </c>
       <c r="B2" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576877</v>
+        <v>576829</v>
       </c>
       <c r="R2" t="n">
-        <v>6509760</v>
+        <v>6509757</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,54 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119718208</v>
+        <v>119718204</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Strupen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576868</v>
+        <v>576855</v>
       </c>
       <c r="R3" t="n">
-        <v>6509665</v>
+        <v>6509782</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119718204</v>
+        <v>119718203</v>
       </c>
       <c r="B4" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576855</v>
+        <v>576877</v>
       </c>
       <c r="R4" t="n">
-        <v>6509782</v>
+        <v>6509760</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -985,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119718220</v>
+        <v>119718208</v>
       </c>
       <c r="B5" t="n">
-        <v>94597</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,34 +977,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Strupen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576829</v>
+        <v>576868</v>
       </c>
       <c r="R5" t="n">
-        <v>6509757</v>
+        <v>6509665</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 39136-2021 artfynd.xlsx
+++ b/artfynd/A 39136-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718220</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718204</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718208</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,8 +1089,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718203</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>